--- a/submissions/team-members/Samsudeen/Csv_data/CropDiseaseClassDistribution.xlsx
+++ b/submissions/team-members/Samsudeen/Csv_data/CropDiseaseClassDistribution.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OWNER\Downloads\Smartleaf Project\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OWNER\Downloads\SDS-CP028-smart-leaf\submissions\team-members\Samsudeen\Csv_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AFA097F-97F5-4792-BE9B-969BB0FFF400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FB3F4C2-0E25-4D5F-997D-F26A0C34B189}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{7A153418-BAB0-4513-944B-FDC24A3425A1}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7A153418-BAB0-4513-944B-FDC24A3425A1}"/>
   </bookViews>
   <sheets>
-    <sheet name="init_clean" sheetId="1" r:id="rId1"/>
-    <sheet name="orig" sheetId="2" r:id="rId2"/>
+    <sheet name="orig" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>Wheat</t>
   </si>
@@ -472,153 +471,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AEB91AC-A867-4DAF-A61C-51FC373DFC12}">
-  <dimension ref="A1:K16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" width="12.54296875" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" customWidth="1"/>
-    <col min="7" max="7" width="10.6328125" customWidth="1"/>
-    <col min="10" max="10" width="13" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>924</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2">
-        <v>282</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="J2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1116</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>902</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>13</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="B11">
-        <f>SUM(B2:B4)</f>
-        <v>2942</v>
-      </c>
-      <c r="E11">
-        <f>SUM(E2:E5)</f>
-        <v>282</v>
-      </c>
-      <c r="H11">
-        <f>SUM(H2:H4)</f>
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <f>SUM(K2:K5)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="G16">
-        <f>SUM(B11:K11)</f>
-        <v>3225</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0BAD1084-7785-43C7-B85B-EC1AB5A58408}">
   <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
